--- a/astro-site/public/dl/restaurant-checklist-templates/09-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/09-cash-drawer-opening-closing.xlsx
@@ -897,11 +897,11 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="47" customHeight="1">
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>▸ In the "Closing Summary" you only type three figures: "Card sales, excl. tips", "Other tenders + card tips paid in cash" and the "POS Z report total". Everything else is a formula.</t>
+          <t>▸ In the "Closing Summary" you only type three figures: "Card sales, excl. tips", "Other tenders + card tips paid in cash" and "POS Z report: sales + tax, excl. tips" (net sales plus sales tax, without tips or gratuities; many POS "total" lines include tips). Everything else is a formula.</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>▸ OVER / SHORT = TOTAL COLLECTED − POS Z report. If the cell turns AMBER, the drawer doesn't balance: check it BEFORE signing.</t>
+          <t>▸ OVER / SHORT = TOTAL COLLECTED − POS Z report (sales + tax, excl. tips). If the cell turns AMBER, the drawer doesn't balance: check it BEFORE signing.</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
     <row r="46" ht="31" customHeight="1">
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
     <row r="50" ht="48" customHeight="1">
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>▸ You are in 09-cash-drawer-opening-closing.xlsx: this is the CASH — the day's MONEY (starting bank, count, POS Z report and over/short); the frame of the day is in 08-restaurant-opening-closing-checklist.xlsx and the detail by zone in 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
+          <t>▸ You are in 09-cash-drawer-opening-closing.xlsx: this is the CASH — the day's MONEY (starting bank, count, POS Z report and over/short); the backbone of the day is in 08-restaurant-opening-closing-checklist.xlsx and the detail by zone in 01-opening-closing-checklists-kitchen-foh-bar.xlsx.</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deducted from cash in the Cash Drawer Closing</t>
+          <t>Deducted from cash on the "Cash Drawer Closing" sheet</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Cash sales (counted − starting bank)</t>
+          <t>Net cash (counted − starting bank)</t>
         </is>
       </c>
       <c r="B49" s="20" t="n"/>
@@ -2355,7 +2355,7 @@
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>POS Z report total</t>
+          <t>POS Z report: sales + tax, excl. tips</t>
         </is>
       </c>
       <c r="B53" s="20" t="n"/>
@@ -2427,7 +2427,7 @@
     <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid mark" error="Use the dropdown: ✓, — or N/A. N/A = not applicable, comes out of the total; — = not done, counts as pending." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid quantity" error="Enter the number of bills or coins: a positive whole number, no decimals." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+    <dataValidation sqref="B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid quantity" error="Enter how many bills, coins or rolls: a whole number (0 or more), no decimals." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>POS Z Report</t>
+          <t>POS Z (+ tax, no tips)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="37" ht="36.75" customHeight="1">
       <c r="A37" s="47" t="inlineStr">
         <is>
-          <t>"Cash Counted" is the drawer count AS IS, with the starting bank inside: Total Collected already deducts it. In TOTALS, "Starting Bank" is the AVERAGE starting bank of the days logged (a balance is not summed) and "Over/Short" is the CUMULATIVE over/short in absolute value: a +50 and a −50 make 100 of over/short, not 0. "Card Sales (no tips)" excludes tips; "Other + Tips Paid" = other tenders + card tips paid in cash from the drawer.</t>
+          <t>"Cash Counted" is the drawer count AS IS, with the starting bank inside: Total Collected already deducts it. In TOTALS, "Starting Bank" is the AVERAGE starting bank of the days logged (a balance is not summed) and "Over/Short" is the CUMULATIVE over/short in absolute value: a +50 and a −50 make 100 of over/short, not 0. "Card Sales (no tips)" excludes tips; "Other + Tips Paid" = other tenders + card tips paid in cash from the drawer. "POS Z" = net sales + sales tax, without tips.</t>
         </is>
       </c>
     </row>
